--- a/manual-qa-test-cases.xlsx
+++ b/manual-qa-test-cases.xlsx
@@ -3,7 +3,8 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Hoja 1" sheetId="1" r:id="rId5"/>
+    <sheet state="visible" name="Test Cases" sheetId="1" r:id="rId5"/>
+    <sheet state="visible" name="Bug Report" sheetId="2" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -11,20 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="53">
+  <si>
+    <t>Bug ID</t>
+  </si>
   <si>
     <t>Test Case ID</t>
   </si>
   <si>
+    <t>Title</t>
+  </si>
+  <si>
     <t>Test Scenario</t>
   </si>
   <si>
+    <t>Environment</t>
+  </si>
+  <si>
     <t>Preconditions</t>
   </si>
   <si>
     <t>Test Steps</t>
   </si>
   <si>
+    <t>Steps to Reproduce</t>
+  </si>
+  <si>
     <t>Test Data</t>
   </si>
   <si>
@@ -34,39 +47,78 @@
     <t>Actual Result</t>
   </si>
   <si>
+    <t>Severity</t>
+  </si>
+  <si>
+    <t>Priority</t>
+  </si>
+  <si>
     <t>Status</t>
   </si>
   <si>
+    <t>Evidence</t>
+  </si>
+  <si>
     <t>Comments</t>
   </si>
   <si>
+    <t>BUG-001</t>
+  </si>
+  <si>
     <t>TC-001</t>
   </si>
   <si>
+    <t>Product remains in cart after removal</t>
+  </si>
+  <si>
     <t>Add product to cart</t>
   </si>
   <si>
     <t>Product is available</t>
   </si>
   <si>
+    <t>Web browser / Demo store</t>
+  </si>
+  <si>
     <t>1. Open the product catalog; 2. Select an available product; 3. Click "Add to Cart"; 4. Open the cart</t>
   </si>
   <si>
+    <t>A product has been added to the cart</t>
+  </si>
+  <si>
     <t>Product: Sample T-shirt</t>
   </si>
   <si>
+    <t>1. Open the cart; 2. Click Remove; 3. Refresh the page</t>
+  </si>
+  <si>
     <t>The selected product appears in the cart with the correct name and price</t>
   </si>
   <si>
+    <t>The product should be removed from the cart</t>
+  </si>
+  <si>
     <t>Not executed</t>
   </si>
   <si>
     <t>Not Run</t>
   </si>
   <si>
+    <t>Illustrative example: product remains visible after refresh</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
     <t>Illustrative test case</t>
   </si>
   <si>
+    <t>Example - Not Reproduced</t>
+  </si>
+  <si>
+    <t>No evidence</t>
+  </si>
+  <si>
     <t>TC-002</t>
   </si>
   <si>
@@ -85,9 +137,15 @@
     <t>TC-003</t>
   </si>
   <si>
+    <t>BUG-002</t>
+  </si>
+  <si>
     <t>Add unavailable product</t>
   </si>
   <si>
+    <t>Unavailable product can be added to cart</t>
+  </si>
+  <si>
     <t>Product is marked as out of stock</t>
   </si>
   <si>
@@ -97,7 +155,22 @@
     <t>Product: Out-of-stock item</t>
   </si>
   <si>
+    <t>A product is marked as unavailable</t>
+  </si>
+  <si>
     <t>The product cannot be added to the cart and its unavailable status is communicated</t>
+  </si>
+  <si>
+    <t>1. Open the product page; 2. Click Add to cart</t>
+  </si>
+  <si>
+    <t>The product should not be added to the cart</t>
+  </si>
+  <si>
+    <t>Illustrative example: product appears in the cart</t>
+  </si>
+  <si>
+    <t>High</t>
   </si>
 </sst>
 </file>
@@ -151,12 +224,18 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
@@ -177,6 +256,10 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -394,163 +477,338 @@
   </cols>
   <sheetData>
     <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="6"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="6"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+    </row>
+    <row r="9">
+      <c r="D9" s="7"/>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="8.0"/>
+    <col customWidth="1" min="2" max="2" width="31.38"/>
+    <col customWidth="1" min="3" max="3" width="20.75"/>
+    <col customWidth="1" min="4" max="4" width="28.38"/>
+    <col customWidth="1" min="5" max="5" width="41.63"/>
+    <col customWidth="1" min="6" max="6" width="34.38"/>
+    <col customWidth="1" min="7" max="7" width="42.63"/>
+    <col customWidth="1" min="8" max="8" width="7.0"/>
+    <col customWidth="1" min="9" max="9" width="6.88"/>
+    <col customWidth="1" min="10" max="10" width="21.13"/>
+    <col customWidth="1" min="11" max="11" width="10.25"/>
+  </cols>
+  <sheetData>
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
-        <v>8</v>
-      </c>
+      <c r="F1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
+      <c r="Q1" s="3"/>
+      <c r="R1" s="3"/>
+      <c r="S1" s="3"/>
+      <c r="T1" s="3"/>
+      <c r="U1" s="3"/>
+      <c r="V1" s="3"/>
+      <c r="W1" s="3"/>
+      <c r="X1" s="3"/>
+      <c r="Y1" s="3"/>
+      <c r="Z1" s="3"/>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" s="2" t="s">
+      <c r="A2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="3" t="s">
-        <v>17</v>
-      </c>
+      <c r="B2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="6"/>
+      <c r="S2" s="6"/>
+      <c r="T2" s="6"/>
+      <c r="U2" s="6"/>
+      <c r="V2" s="6"/>
+      <c r="W2" s="6"/>
+      <c r="X2" s="6"/>
+      <c r="Y2" s="6"/>
+      <c r="Z2" s="6"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" s="2" t="s">
+      <c r="A3" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="4"/>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-    </row>
-    <row r="9">
-      <c r="D9" s="5"/>
+      <c r="D3" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6"/>
+      <c r="U3" s="6"/>
+      <c r="V3" s="6"/>
+      <c r="W3" s="6"/>
+      <c r="X3" s="6"/>
+      <c r="Y3" s="6"/>
+      <c r="Z3" s="6"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
